--- a/branches/dev/v2027/StructureDefinition-mii-pr-patho-base-observation.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-patho-base-observation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:30:15+00:00</t>
+    <t>2026-09-14T08:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1450,7 +1450,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-biobank/ValueSet/sct-body-structures</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-biobank/ValueSet/mii-vs-biobank-body-structures-sct</t>
   </si>
   <si>
     <t>Observation.bodySite.coding:sct.id</t>
@@ -2247,7 +2247,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="76.8671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="88.984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-patho-base-observation.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-patho-base-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:48:26+00:00</t>
+    <t>2026-09-14T10:17:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-patho-base-observation.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-patho-base-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T10:17:23+00:00</t>
+    <t>2026-09-14T10:33:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
